--- a/artfynd/A 25683-2026 artfynd.xlsx
+++ b/artfynd/A 25683-2026 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>87047730</v>
       </c>
       <c r="B2" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>412023.7835616084</v>
+        <v>412024</v>
       </c>
       <c r="R2" t="n">
-        <v>6971381.106150837</v>
+        <v>6971381</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,19 +747,9 @@
           <t>2020-07-07</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-07-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">

--- a/artfynd/A 25683-2026 artfynd.xlsx
+++ b/artfynd/A 25683-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -783,6 +783,108 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>135121212</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Röverfallet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>411872</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6971463</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25683-2026 artfynd.xlsx
+++ b/artfynd/A 25683-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -885,6 +885,220 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135463012</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>A 25683-2026, Hjd</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>411892</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6971406</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135463024</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>A 25683-2026, Hjd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>411892</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6971406</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25683-2026 artfynd.xlsx
+++ b/artfynd/A 25683-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -782,6 +787,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87047730</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135121212</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135463012</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1098,8 +1118,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135463024</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 25683-2026 artfynd.xlsx
+++ b/artfynd/A 25683-2026 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>135121212</v>
       </c>
       <c r="B3" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>135463012</v>
       </c>
       <c r="B4" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135463024</v>
       </c>
       <c r="B5" t="n">
-        <v>58131</v>
+        <v>58136</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 25683-2026 artfynd.xlsx
+++ b/artfynd/A 25683-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -900,10 +900,236 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135463012</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>A 25683-2026, Hjd</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>411892</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6971406</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135463012</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135463024</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>A 25683-2026, Hjd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>411892</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6971406</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135463024</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25683-2026 artfynd.xlsx
+++ b/artfynd/A 25683-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135121212</v>
+        <v>135463012</v>
       </c>
       <c r="B3" t="n">
-        <v>57980</v>
+        <v>58141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,34 +806,46 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Röverfallet, Hjd</t>
+          <t>A 25683-2026, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>411872</v>
+        <v>411892</v>
       </c>
       <c r="R3" t="n">
-        <v>6971463</v>
+        <v>6971406</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,17 +872,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,49 +892,49 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135121212</t>
+          <t>https://artportalen.se/Sighting/135463012</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135463012</v>
+        <v>135463024</v>
       </c>
       <c r="B4" t="n">
-        <v>58141</v>
+        <v>58136</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>103023</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -937,11 +944,7 @@
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -1009,116 +1012,6 @@
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135463012</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>135463024</v>
-      </c>
-      <c r="B5" t="n">
-        <v>58136</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>103023</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Tofsmes</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Lophophanes cristatus</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>A 25683-2026, Hjd</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>411892</v>
-      </c>
-      <c r="R5" t="n">
-        <v>6971406</v>
-      </c>
-      <c r="S5" t="n">
-        <v>10</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Christer Johansson</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Christer Johansson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
-      <c r="AZ5" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135463024</t>
         </is>
@@ -1129,7 +1022,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25683-2026 artfynd.xlsx
+++ b/artfynd/A 25683-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135463012</v>
+        <v>135121212</v>
       </c>
       <c r="B3" t="n">
-        <v>58141</v>
+        <v>57980</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,46 +806,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 25683-2026, Hjd</t>
+          <t>Röverfallet, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>411892</v>
+        <v>411872</v>
       </c>
       <c r="R3" t="n">
-        <v>6971406</v>
+        <v>6971463</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,12 +860,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,49 +885,49 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135463012</t>
+          <t>https://artportalen.se/Sighting/135121212</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135463024</v>
+        <v>135463012</v>
       </c>
       <c r="B4" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -944,7 +937,11 @@
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -1012,6 +1009,116 @@
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135463012</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135463024</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>A 25683-2026, Hjd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>411892</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6971406</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135463024</t>
         </is>
@@ -1022,6 +1129,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25683-2026 artfynd.xlsx
+++ b/artfynd/A 25683-2026 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>135121212</v>
       </c>
       <c r="B3" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>135463012</v>
       </c>
       <c r="B4" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135463024</v>
       </c>
       <c r="B5" t="n">
-        <v>58136</v>
+        <v>58138</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 25683-2026 artfynd.xlsx
+++ b/artfynd/A 25683-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135121212</v>
+        <v>135463012</v>
       </c>
       <c r="B3" t="n">
-        <v>57982</v>
+        <v>58143</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,34 +806,46 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Röverfallet, Hjd</t>
+          <t>A 25683-2026, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>411872</v>
+        <v>411892</v>
       </c>
       <c r="R3" t="n">
-        <v>6971463</v>
+        <v>6971406</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,17 +872,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,49 +892,49 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135121212</t>
+          <t>https://artportalen.se/Sighting/135463012</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135463012</v>
+        <v>135463024</v>
       </c>
       <c r="B4" t="n">
-        <v>58143</v>
+        <v>58138</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>103023</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -937,11 +944,7 @@
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -1009,116 +1012,6 @@
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135463012</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>135463024</v>
-      </c>
-      <c r="B5" t="n">
-        <v>58138</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>103023</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Tofsmes</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Lophophanes cristatus</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>A 25683-2026, Hjd</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>411892</v>
-      </c>
-      <c r="R5" t="n">
-        <v>6971406</v>
-      </c>
-      <c r="S5" t="n">
-        <v>10</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Christer Johansson</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Christer Johansson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
-      <c r="AZ5" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135463024</t>
         </is>
@@ -1129,7 +1022,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25683-2026 artfynd.xlsx
+++ b/artfynd/A 25683-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135463012</v>
+        <v>135121212</v>
       </c>
       <c r="B3" t="n">
-        <v>58143</v>
+        <v>57982</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,46 +806,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 25683-2026, Hjd</t>
+          <t>Röverfallet, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>411892</v>
+        <v>411872</v>
       </c>
       <c r="R3" t="n">
-        <v>6971406</v>
+        <v>6971463</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,12 +860,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,49 +885,49 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135463012</t>
+          <t>https://artportalen.se/Sighting/135121212</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135463024</v>
+        <v>135463012</v>
       </c>
       <c r="B4" t="n">
-        <v>58138</v>
+        <v>58143</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -944,7 +937,11 @@
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -1012,6 +1009,116 @@
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135463012</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135463024</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58138</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>A 25683-2026, Hjd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>411892</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6971406</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135463024</t>
         </is>
@@ -1022,6 +1129,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25683-2026 artfynd.xlsx
+++ b/artfynd/A 25683-2026 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>135121212</v>
       </c>
       <c r="B3" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 25683-2026 artfynd.xlsx
+++ b/artfynd/A 25683-2026 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>135121212</v>
       </c>
       <c r="B3" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 25683-2026 artfynd.xlsx
+++ b/artfynd/A 25683-2026 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>135121212</v>
       </c>
       <c r="B3" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 25683-2026 artfynd.xlsx
+++ b/artfynd/A 25683-2026 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>135121212</v>
       </c>
       <c r="B3" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 25683-2026 artfynd.xlsx
+++ b/artfynd/A 25683-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135121212</v>
+        <v>135463012</v>
       </c>
       <c r="B3" t="n">
-        <v>57993</v>
+        <v>58143</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,34 +806,46 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Röverfallet, Hjd</t>
+          <t>A 25683-2026, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>411872</v>
+        <v>411892</v>
       </c>
       <c r="R3" t="n">
-        <v>6971463</v>
+        <v>6971406</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,17 +872,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,49 +892,49 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135121212</t>
+          <t>https://artportalen.se/Sighting/135463012</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135463012</v>
+        <v>135463024</v>
       </c>
       <c r="B4" t="n">
-        <v>58143</v>
+        <v>58138</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>103023</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -937,11 +944,7 @@
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -1009,116 +1012,6 @@
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135463012</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>135463024</v>
-      </c>
-      <c r="B5" t="n">
-        <v>58138</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>103023</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Tofsmes</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Lophophanes cristatus</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>A 25683-2026, Hjd</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>411892</v>
-      </c>
-      <c r="R5" t="n">
-        <v>6971406</v>
-      </c>
-      <c r="S5" t="n">
-        <v>10</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Christer Johansson</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Christer Johansson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
-      <c r="AZ5" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135463024</t>
         </is>
@@ -1129,7 +1022,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25683-2026 artfynd.xlsx
+++ b/artfynd/A 25683-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135463012</v>
+        <v>135121212</v>
       </c>
       <c r="B3" t="n">
-        <v>58143</v>
+        <v>58006</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,46 +806,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 25683-2026, Hjd</t>
+          <t>Röverfallet, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>411892</v>
+        <v>411872</v>
       </c>
       <c r="R3" t="n">
-        <v>6971406</v>
+        <v>6971463</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,12 +860,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,49 +885,49 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135463012</t>
+          <t>https://artportalen.se/Sighting/135121212</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135463024</v>
+        <v>135463012</v>
       </c>
       <c r="B4" t="n">
-        <v>58138</v>
+        <v>58143</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -944,7 +937,11 @@
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -1012,6 +1009,116 @@
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135463012</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135463024</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58138</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>A 25683-2026, Hjd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>411892</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6971406</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135463024</t>
         </is>
@@ -1022,6 +1129,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
